--- a/results/feature_selection/global/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/qP_calc/metrics_global.xlsx
@@ -488,46 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, I, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.493479705977017</v>
+        <v>0.9497190193435032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001213096836208276</v>
+        <v>0.0006069152344820548</v>
       </c>
       <c r="F2" t="n">
-        <v>1.225868864921858e-05</v>
+        <v>1.236451250993631e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003501241015585557</v>
+        <v>0.001111958295528043</v>
       </c>
       <c r="H2" t="n">
-        <v>660.0472044640106</v>
+        <v>531.073071255742</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1544646692889494</v>
+        <v>0.01658515971282473</v>
       </c>
       <c r="J2" t="n">
-        <v>-1414.968724957993</v>
+        <v>-1680.804881793889</v>
       </c>
       <c r="K2" t="n">
-        <v>-1400.787315423235</v>
+        <v>-1672.344037097074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,116 +535,116 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.279828085239733</v>
+        <v>0.9488106925641332</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002194053788876231</v>
+        <v>0.0006254169473457643</v>
       </c>
       <c r="F3" t="n">
-        <v>1.742943645325515e-05</v>
+        <v>1.25878776408465e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004174857656645931</v>
+        <v>0.001121957113300081</v>
       </c>
       <c r="H3" t="n">
-        <v>663.8355530946093</v>
+        <v>593.6042478527182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2175637750335974</v>
+        <v>0.0168576733821949</v>
       </c>
       <c r="J3" t="n">
-        <v>-1374.626103900225</v>
+        <v>-1678.58481262099</v>
       </c>
       <c r="K3" t="n">
-        <v>-1366.11725817937</v>
+        <v>-1670.123967924175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2766924366497884</v>
+        <v>0.8173318137804548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002249895678979234</v>
+        <v>0.001032855018861098</v>
       </c>
       <c r="F4" t="n">
-        <v>1.750532470537669e-05</v>
+        <v>4.491963052807143e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004183936508286985</v>
+        <v>0.00211942517037218</v>
       </c>
       <c r="H4" t="n">
-        <v>736.6007374054094</v>
+        <v>1136.462426927583</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2190045227323573</v>
+        <v>0.05630360024000053</v>
       </c>
       <c r="J4" t="n">
-        <v>-1372.078687259002</v>
+        <v>-1520.839372532721</v>
       </c>
       <c r="K4" t="n">
-        <v>-1360.733559631196</v>
+        <v>-1512.378527835906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2490896137175614</v>
+        <v>0.8094984370301773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002063542309054858</v>
+        <v>0.001021380258354805</v>
       </c>
       <c r="F5" t="n">
-        <v>1.817336193144355e-05</v>
+        <v>4.684592320492946e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004263022628539936</v>
+        <v>0.002164391905476674</v>
       </c>
       <c r="H5" t="n">
-        <v>682.5245894240783</v>
+        <v>1181.712448787594</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2267858372380836</v>
+        <v>0.05765374810557116</v>
       </c>
       <c r="J5" t="n">
-        <v>-1369.359761938033</v>
+        <v>-1519.632726348148</v>
       </c>
       <c r="K5" t="n">
-        <v>-1360.850916217179</v>
+        <v>-1516.812444782543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,77 +652,77 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01434889217277691</v>
+        <v>0.7982968910715966</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002020460785575279</v>
+        <v>0.001009988253151244</v>
       </c>
       <c r="F6" t="n">
-        <v>2.385450334407145e-05</v>
+        <v>4.960047678218956e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004884107220779602</v>
+        <v>0.00222711644918243</v>
       </c>
       <c r="H6" t="n">
-        <v>1991.436013255307</v>
+        <v>981.0285493790136</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2962120305005078</v>
+        <v>0.06101440471189577</v>
       </c>
       <c r="J6" t="n">
-        <v>-1339.085729913515</v>
+        <v>-1512.547805386457</v>
       </c>
       <c r="K6" t="n">
-        <v>-1336.249448006564</v>
+        <v>-1509.727523820852</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, T</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.008564224695078448</v>
+        <v>0.785187288401262</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001736878460602909</v>
+        <v>0.00118791647583778</v>
       </c>
       <c r="F7" t="n">
-        <v>2.399450254723299e-05</v>
+        <v>5.282423741894042e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004898418372008764</v>
+        <v>0.002298352397238953</v>
       </c>
       <c r="H7" t="n">
-        <v>850.0636692185974</v>
+        <v>1586.403127250633</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3004475287432596</v>
+        <v>0.06544751117624076</v>
       </c>
       <c r="J7" t="n">
-        <v>-1328.348412612719</v>
+        <v>-1502.739564919986</v>
       </c>
       <c r="K7" t="n">
-        <v>-1311.33072117101</v>
+        <v>-1497.099001788776</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -730,110 +730,110 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1720876423774409</v>
+        <v>-0.31817109877437</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003769825340669269</v>
+        <v>0.005128281123827074</v>
       </c>
       <c r="F8" t="n">
-        <v>2.836659783832818e-05</v>
+        <v>3.241492673418306e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005326030213801662</v>
+        <v>0.005693410817267893</v>
       </c>
       <c r="H8" t="n">
-        <v>1391.897828875949</v>
+        <v>3643.073971866525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7062922986634382</v>
+        <v>0.79394804016205</v>
       </c>
       <c r="J8" t="n">
-        <v>-1313.25757791705</v>
+        <v>-1275.774550908429</v>
       </c>
       <c r="K8" t="n">
-        <v>-1304.748732196196</v>
+        <v>-1267.313706211614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.3098184711346113</v>
+        <v>-0.421368320212822</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004415992097902281</v>
+        <v>0.005419394526733596</v>
       </c>
       <c r="F9" t="n">
-        <v>3.169992794781513e-05</v>
+        <v>3.49526324805835e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005630268905462254</v>
+        <v>0.005912075141655719</v>
       </c>
       <c r="H9" t="n">
-        <v>2489.968959690515</v>
+        <v>3678.841643798832</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7919354625798939</v>
+        <v>0.8548699258131661</v>
       </c>
       <c r="J9" t="n">
-        <v>-1293.258714902924</v>
+        <v>-1268.428079577725</v>
       </c>
       <c r="K9" t="n">
-        <v>-1276.241023461215</v>
+        <v>-1262.787516446515</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3314245298273479</v>
+        <v>-2.318983542409569</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004216706996742206</v>
+        <v>0.00879335170918083</v>
       </c>
       <c r="F10" t="n">
-        <v>3.222283285325804e-05</v>
+        <v>8.161657349277138e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005676515907954283</v>
+        <v>0.009034189144177323</v>
       </c>
       <c r="H10" t="n">
-        <v>1292.963437704914</v>
+        <v>4349.850606849895</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8048998298624034</v>
+        <v>1.993504388648632</v>
       </c>
       <c r="J10" t="n">
-        <v>-1291.197242997029</v>
+        <v>-1163.271298050973</v>
       </c>
       <c r="K10" t="n">
-        <v>-1274.17955155532</v>
+        <v>-1157.630734919763</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/qP_calc/metrics_global.xlsx
@@ -488,40 +488,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>T, I, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9497190193435032</v>
+        <v>0.4947698325742224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006069152344820548</v>
+        <v>0.001204865780912384</v>
       </c>
       <c r="F2" t="n">
-        <v>1.236451250993631e-06</v>
+        <v>1.242403120219518e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001111958295528043</v>
+        <v>0.003524773922139572</v>
       </c>
       <c r="H2" t="n">
-        <v>531.073071255742</v>
+        <v>662.8009972837284</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01658515971282473</v>
+        <v>0.1540777470495749</v>
       </c>
       <c r="J2" t="n">
-        <v>-1680.804881793889</v>
+        <v>-1390.688867123804</v>
       </c>
       <c r="K2" t="n">
-        <v>-1672.344037097074</v>
+        <v>-1376.587459295779</v>
       </c>
     </row>
     <row r="3">
@@ -535,38 +535,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9488106925641332</v>
+        <v>0.2832870705107874</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006254169473457643</v>
+        <v>0.002227051772162193</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25878776408465e-06</v>
+        <v>1.762456870768476e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001121957113300081</v>
+        <v>0.004198162539455179</v>
       </c>
       <c r="H3" t="n">
-        <v>593.6042478527182</v>
+        <v>658.3105600422638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0168576733821949</v>
+        <v>0.2165262160448592</v>
       </c>
       <c r="J3" t="n">
-        <v>-1678.58481262099</v>
+        <v>-1351.330868326364</v>
       </c>
       <c r="K3" t="n">
-        <v>-1670.123967924175</v>
+        <v>-1342.870023629549</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,71 +574,71 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1, V_calc</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8173318137804548</v>
+        <v>0.2819719167560885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001032855018861098</v>
+        <v>0.002212001595706386</v>
       </c>
       <c r="F4" t="n">
-        <v>4.491963052807143e-06</v>
+        <v>1.765690943541152e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00211942517037218</v>
+        <v>0.004202012545841757</v>
       </c>
       <c r="H4" t="n">
-        <v>1136.462426927583</v>
+        <v>661.2227126014021</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05630360024000053</v>
+        <v>0.2169207848097783</v>
       </c>
       <c r="J4" t="n">
-        <v>-1520.839372532721</v>
+        <v>-1351.103539338329</v>
       </c>
       <c r="K4" t="n">
-        <v>-1512.378527835906</v>
+        <v>-1342.642694641514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8094984370301773</v>
+        <v>0.253462768570904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001021380258354805</v>
+        <v>0.002086002514830899</v>
       </c>
       <c r="F5" t="n">
-        <v>4.684592320492946e-06</v>
+        <v>1.835797316722594e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002164391905476674</v>
+        <v>0.004284620539467403</v>
       </c>
       <c r="H5" t="n">
-        <v>1181.712448787594</v>
+        <v>687.3111965842984</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05765374810557116</v>
+        <v>0.2254740200099459</v>
       </c>
       <c r="J5" t="n">
-        <v>-1519.632726348148</v>
+        <v>-1346.275375028159</v>
       </c>
       <c r="K5" t="n">
-        <v>-1516.812444782543</v>
+        <v>-1337.814530331344</v>
       </c>
     </row>
     <row r="6">
@@ -648,36 +648,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7982968910715966</v>
+        <v>0.02976081058491364</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001009988253151244</v>
+        <v>0.001700014551674668</v>
       </c>
       <c r="F6" t="n">
-        <v>4.960047678218956e-06</v>
+        <v>2.385899089182252e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00222711644918243</v>
+        <v>0.004884566602250656</v>
       </c>
       <c r="H6" t="n">
-        <v>981.0285493790136</v>
+        <v>841.7762263425958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06101440471189577</v>
+        <v>0.2935884581181503</v>
       </c>
       <c r="J6" t="n">
-        <v>-1512.547805386457</v>
+        <v>-1309.775329948856</v>
       </c>
       <c r="K6" t="n">
-        <v>-1509.727523820852</v>
+        <v>-1295.67392212083</v>
       </c>
     </row>
     <row r="7">
@@ -687,42 +687,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.785187288401262</v>
+        <v>0.0172412790177604</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00118791647583778</v>
+        <v>0.002019595152684177</v>
       </c>
       <c r="F7" t="n">
-        <v>5.282423741894042e-06</v>
+        <v>2.416685661492392e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002298352397238953</v>
+        <v>0.004915979720760036</v>
       </c>
       <c r="H7" t="n">
-        <v>1586.403127250633</v>
+        <v>2098.579102051984</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06544751117624076</v>
+        <v>0.2953445330943024</v>
       </c>
       <c r="J7" t="n">
-        <v>-1502.739564919986</v>
+        <v>-1316.18552468447</v>
       </c>
       <c r="K7" t="n">
-        <v>-1497.099001788776</v>
+        <v>-1313.365243118865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -730,32 +730,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.31817109877437</v>
+        <v>-0.1704966190456332</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005128281123827074</v>
+        <v>0.004236874283225835</v>
       </c>
       <c r="F8" t="n">
-        <v>3.241492673418306e-05</v>
+        <v>2.878348811034387e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005693410817267893</v>
+        <v>0.005365024520945256</v>
       </c>
       <c r="H8" t="n">
-        <v>3643.073971866525</v>
+        <v>1060.490862794406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.79394804016205</v>
+        <v>0.7053382683107345</v>
       </c>
       <c r="J8" t="n">
-        <v>-1275.774550908429</v>
+        <v>-1290.507874427825</v>
       </c>
       <c r="K8" t="n">
-        <v>-1267.313706211614</v>
+        <v>-1282.04702973101</v>
       </c>
     </row>
     <row r="9">
@@ -765,75 +765,75 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.421368320212822</v>
+        <v>-0.3038584184556474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005419394526733596</v>
+        <v>0.004220376408485179</v>
       </c>
       <c r="F9" t="n">
-        <v>3.49526324805835e-05</v>
+        <v>3.206296598771018e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005912075141655719</v>
+        <v>0.005662416974023564</v>
       </c>
       <c r="H9" t="n">
-        <v>3678.841643798832</v>
+        <v>1309.668641491634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8548699258131661</v>
+        <v>0.7883599392257714</v>
       </c>
       <c r="J9" t="n">
-        <v>-1268.428079577725</v>
+        <v>-1271.128303774734</v>
       </c>
       <c r="K9" t="n">
-        <v>-1262.787516446515</v>
+        <v>-1254.206614381104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.318983542409569</v>
+        <v>-0.5786139407468143</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00879335170918083</v>
+        <v>0.004708437279163661</v>
       </c>
       <c r="F10" t="n">
-        <v>8.161657349277138e-05</v>
+        <v>3.881943343959164e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009034189144177323</v>
+        <v>0.006230524331032793</v>
       </c>
       <c r="H10" t="n">
-        <v>4349.850606849895</v>
+        <v>1628.240573655918</v>
       </c>
       <c r="I10" t="n">
-        <v>1.993504388648632</v>
+        <v>0.9542227116549041</v>
       </c>
       <c r="J10" t="n">
-        <v>-1163.271298050973</v>
+        <v>-1245.417107285037</v>
       </c>
       <c r="K10" t="n">
-        <v>-1157.630734919763</v>
+        <v>-1225.675136325802</v>
       </c>
     </row>
   </sheetData>
